--- a/devices/digiIX20/IP_TEMPLATE.xlsx
+++ b/devices/digiIX20/IP_TEMPLATE.xlsx
@@ -131,7 +131,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
@@ -207,6 +207,15 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -1154,28 +1163,28 @@
       <c r="F2" s="1" t="n">
         <v>3754160</v>
       </c>
-      <c r="G2" s="12" t="inlineStr">
-        <is>
-          <t>20:97:27:17:9E:4B</t>
-        </is>
-      </c>
-      <c r="H2" s="17" t="n">
-        <v>46176.30628055555</v>
-      </c>
-      <c r="I2" s="10" t="inlineStr">
-        <is>
-          <t>label_JKC-SLC_10000_2026-04-22_15-06-46.txt</t>
+      <c r="G2" s="30" t="inlineStr">
+        <is>
+          <t>00:04:F3:B2:3B:E8</t>
+        </is>
+      </c>
+      <c r="H2" s="31" t="inlineStr">
+        <is>
+          <t>2026-08-04 15:08:52</t>
+        </is>
+      </c>
+      <c r="I2" s="27" t="inlineStr">
+        <is>
+          <t>label_digiIX20_IP_TEMPLATE_10000_2026-08-04_15-08-52.txt</t>
         </is>
       </c>
       <c r="J2" s="10" t="inlineStr">
         <is>
-          <t>../../../../u317029/Documents/teltonika/crash_logs/crash_log_JKC-SLC_10000_2026-04-22_15-36-53.txt</t>
-        </is>
-      </c>
-      <c r="K2" s="11" t="inlineStr">
-        <is>
-          <t>Not Tested</t>
-        </is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="K2" s="28" t="n">
+        <v>1</v>
       </c>
       <c r="L2" s="13" t="n">
         <v>46134.66675111111</v>
@@ -1274,23 +1283,23 @@
           <t>20:97:27:17:9E:4B</t>
         </is>
       </c>
-      <c r="H4" s="17" t="n">
-        <v>46196.52679668982</v>
+      <c r="H4" s="29" t="inlineStr">
+        <is>
+          <t>2026-08-04 14:48:24</t>
+        </is>
       </c>
       <c r="I4" s="18" t="inlineStr">
         <is>
           <t>label_IP_TEMPLATE_10002_2026-06-03_10-01-52.txt</t>
         </is>
       </c>
-      <c r="J4" s="18" t="inlineStr">
-        <is>
-          <t>../../../../admin/Documents/teltonika/crash_logs/crash_log_IP_TEMPLATE_10002_2026-06-17_15-54-02.txt</t>
-        </is>
-      </c>
-      <c r="K4" s="23" t="inlineStr">
-        <is>
-          <t>Not Tested</t>
-        </is>
+      <c r="J4" s="27" t="inlineStr">
+        <is>
+          <t>crash_log_digiIX20_IP_TEMPLATE_10002_2026-08-04_14-48-24.txt</t>
+        </is>
+      </c>
+      <c r="K4" s="28" t="n">
+        <v>1</v>
       </c>
       <c r="L4" s="17" t="n">
         <v>46196.52679421296</v>
